--- a/results/assessment/vIAbility/features/markers/ML/iter3/cv_results.xlsx
+++ b/results/assessment/vIAbility/features/markers/ML/iter3/cv_results.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -558,646 +558,560 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GaussianNB</t>
+          <t>SVC</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5178</v>
+        <v>0.5173</v>
       </c>
       <c r="C3" t="n">
-        <v>0.384</v>
+        <v>0.3955</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3</v>
+        <v>0.4101</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3627</v>
+        <v>0.3939</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3357</v>
+        <v>0.3962</v>
       </c>
       <c r="G3" t="n">
-        <v>0.485</v>
+        <v>0.4844</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0673</v>
+        <v>0.0283</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1053</v>
+        <v>0.0535</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0788</v>
+        <v>0.1403</v>
       </c>
       <c r="K3" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.0732</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0866</v>
+        <v>0.0993</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0307</v>
+        <v>0.0663</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>GaussianNB</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5348000000000001</v>
+        <v>0.5178</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4336</v>
+        <v>0.384</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4359</v>
+        <v>0.3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4295</v>
+        <v>0.3627</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4279</v>
+        <v>0.3357</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5001</v>
+        <v>0.485</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0785</v>
+        <v>0.0673</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0906</v>
+        <v>0.1053</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1267</v>
+        <v>0.0788</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0858</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0925</v>
+        <v>0.0866</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0707</v>
+        <v>0.0307</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MLPClassifier</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4131</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>0.408</v>
+        <v>0.4336</v>
       </c>
       <c r="D5" t="n">
-        <v>0.983</v>
+        <v>0.4359</v>
       </c>
       <c r="E5" t="n">
-        <v>0.462</v>
+        <v>0.4295</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5765</v>
+        <v>0.4279</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4976</v>
+        <v>0.5001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0277</v>
+        <v>0.0785</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0154</v>
+        <v>0.0906</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0209</v>
+        <v>0.1267</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0162</v>
+        <v>0.0858</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0169</v>
+        <v>0.0925</v>
       </c>
       <c r="M5" t="n">
-        <v>0.075</v>
+        <v>0.0707</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>MLPClassifier</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5174</v>
+        <v>0.4131</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4218</v>
+        <v>0.408</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4949</v>
+        <v>0.983</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4305</v>
+        <v>0.462</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4488</v>
+        <v>0.5765</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.4976</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0298</v>
+        <v>0.0277</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0248</v>
+        <v>0.0154</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1071</v>
+        <v>0.0209</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0284</v>
+        <v>0.0162</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0535</v>
+        <v>0.0169</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0103</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TabPFN</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5799</v>
+        <v>0.5174</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1333</v>
+        <v>0.4218</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0174</v>
+        <v>0.4949</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0571</v>
+        <v>0.4305</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0308</v>
+        <v>0.4488</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4775</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0152</v>
+        <v>0.0298</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1633</v>
+        <v>0.0248</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0213</v>
+        <v>0.1071</v>
       </c>
       <c r="K7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0284</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0377</v>
+        <v>0.0535</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0171</v>
+        <v>0.0103</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bagging_RandomForest</t>
+          <t>TabPFN</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5141</v>
+        <v>0.5799</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3177</v>
+        <v>0.1333</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1877</v>
+        <v>0.0174</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2762</v>
+        <v>0.0571</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2334</v>
+        <v>0.0308</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4928</v>
+        <v>0.4775</v>
       </c>
       <c r="H8" t="n">
-        <v>0.056</v>
+        <v>0.0152</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1248</v>
+        <v>0.1633</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0978</v>
+        <v>0.0213</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1168</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1088</v>
+        <v>0.0377</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0525</v>
+        <v>0.0171</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bagging_SVC</t>
+          <t>Bagging_RandomForest</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5209</v>
+        <v>0.5141</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3809</v>
+        <v>0.3177</v>
       </c>
       <c r="D9" t="n">
-        <v>0.392</v>
+        <v>0.1877</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3805</v>
+        <v>0.2762</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3829</v>
+        <v>0.2334</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5223</v>
+        <v>0.4928</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0459</v>
+        <v>0.056</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1127</v>
+        <v>0.1248</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1645</v>
+        <v>0.0978</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1261</v>
+        <v>0.1168</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1422</v>
+        <v>0.1088</v>
       </c>
       <c r="M9" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.0525</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bagging_GaussianNB</t>
+          <t>Bagging_SVC</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5489000000000001</v>
+        <v>0.5209</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4467</v>
+        <v>0.3809</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3333</v>
+        <v>0.392</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4113</v>
+        <v>0.3805</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3742</v>
+        <v>0.3829</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5048</v>
+        <v>0.5223</v>
       </c>
       <c r="H10" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.0459</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0935</v>
+        <v>0.1127</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0688</v>
+        <v>0.1645</v>
       </c>
       <c r="K10" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.1261</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.1422</v>
       </c>
       <c r="M10" t="n">
-        <v>0.045</v>
+        <v>0.07820000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bagging_DecisionTree</t>
+          <t>Bagging_GaussianNB</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5105</v>
+        <v>0.5489000000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>0.357</v>
+        <v>0.4467</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2732</v>
+        <v>0.3333</v>
       </c>
       <c r="E11" t="n">
-        <v>0.335</v>
+        <v>0.4113</v>
       </c>
       <c r="F11" t="n">
-        <v>0.308</v>
+        <v>0.3742</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5056</v>
+        <v>0.5048</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0287</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0569</v>
+        <v>0.0935</v>
       </c>
       <c r="J11" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.0688</v>
       </c>
       <c r="K11" t="n">
-        <v>0.064</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0462</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bagging_MLPClassifier</t>
+          <t>Bagging_DecisionTree</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4062</v>
+        <v>0.5105</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4062</v>
+        <v>0.357</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0.2732</v>
       </c>
       <c r="E12" t="n">
-        <v>0.461</v>
+        <v>0.335</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5777</v>
+        <v>0.308</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4845</v>
+        <v>0.5056</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0067</v>
+        <v>0.0287</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0067</v>
+        <v>0.0569</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0069</v>
+        <v>0.064</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0068</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0619</v>
+        <v>0.0462</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Bagging_LogisticRegression</t>
+          <t>Bagging_MLPClassifier</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5174</v>
+        <v>0.4062</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4179</v>
+        <v>0.4062</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4779</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4277</v>
+        <v>0.461</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4443</v>
+        <v>0.5777</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.4845</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0305</v>
+        <v>0.0067</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0353</v>
+        <v>0.0067</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0675</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0368</v>
+        <v>0.0069</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0442</v>
+        <v>0.0068</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0119</v>
+        <v>0.0619</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bagging_TabPFN</t>
+          <t>Bagging_LogisticRegression</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5833</v>
+        <v>0.5174</v>
       </c>
       <c r="C14" t="n">
-        <v>0.43</v>
+        <v>0.4179</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0594</v>
+        <v>0.4779</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1875</v>
+        <v>0.4277</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1034</v>
+        <v>0.4443</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5081</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>0.016</v>
+        <v>0.0305</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1439</v>
+        <v>0.0353</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0195</v>
+        <v>0.0675</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0564</v>
+        <v>0.0368</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0326</v>
+        <v>0.0442</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0246</v>
+        <v>0.0119</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Voting_soft_SVC+DecisionTree+LogisticRegression</t>
+          <t>Bagging_TabPFN</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5209</v>
+        <v>0.5833</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4058</v>
+        <v>0.43</v>
       </c>
       <c r="D15" t="n">
-        <v>0.367</v>
+        <v>0.0594</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3924</v>
+        <v>0.1875</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3784</v>
+        <v>0.1034</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5209</v>
+        <v>0.5081</v>
       </c>
       <c r="H15" t="n">
-        <v>0.064</v>
+        <v>0.016</v>
       </c>
       <c r="I15" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.1439</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1093</v>
+        <v>0.0195</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0721</v>
+        <v>0.0564</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0799</v>
+        <v>0.0326</v>
       </c>
       <c r="M15" t="n">
-        <v>0.08019999999999999</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Voting_soft_SVC+GaussianNB+DecisionTree+MLPClassifier+TabPFN</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.5105</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.3975</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.3678</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.3883</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.3778</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.4915</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.0716</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.0858</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.0692</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.0689</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.0693</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Voting_soft_SVC+GaussianNB+DecisionTree+MLPClassifier+LogisticRegression+TabPFN</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.5036</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.3902</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.3928</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.3865</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.3851</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.5004</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.0497</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.1092</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.0452</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.0658</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.068</v>
+        <v>0.0246</v>
       </c>
     </row>
   </sheetData>
@@ -1211,7 +1125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1608,156 +1522,6 @@
       </c>
       <c r="G15" t="n">
         <v>0.5838</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Voting_hard_DecisionTree+MLPClassifier+LogisticRegression</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.5165</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.4419</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.4872</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.4502</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.4634</v>
-      </c>
-      <c r="G16" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Voting_hard_RandomForest+SVC+DecisionTree</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.5275</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.4412</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.3846</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.4286</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.411</v>
-      </c>
-      <c r="G17" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Voting_hard_RandomForest+SVC+DecisionTree+MLPClassifier</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0.4945</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.3478</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.2051</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.3053</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.2581</v>
-      </c>
-      <c r="G18" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Voting_soft_SVC+DecisionTree+LogisticRegression</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0.5054999999999999</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.4118</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.359</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.3836</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.5222</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Voting_soft_SVC+GaussianNB+DecisionTree+MLPClassifier+TabPFN</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0.4945</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.3793</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.2821</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.3548</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.3235</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.5385</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Voting_soft_SVC+GaussianNB+DecisionTree+MLPClassifier+LogisticRegression+TabPFN</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0.5054999999999999</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.3077</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.3774</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.3478</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.5557</v>
       </c>
     </row>
   </sheetData>
